--- a/Gantt.xlsx
+++ b/Gantt.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Diagramme de gantt</t>
   </si>
@@ -44,6 +44,9 @@
     <t xml:space="preserve">Date de fin du projet : </t>
   </si>
   <si>
+    <t>Effectif</t>
+  </si>
+  <si>
     <t>Début</t>
   </si>
   <si>
@@ -53,6 +56,9 @@
     <t>Livrables techniques</t>
   </si>
   <si>
+    <t>Milhane</t>
+  </si>
+  <si>
     <t>Projet : JADE - Justice Algorithmique des Élections</t>
   </si>
   <si>
@@ -96,6 +102,15 @@
   </si>
   <si>
     <t>Debugging et robustesse du code</t>
+  </si>
+  <si>
+    <t>Milhane, Mahdi</t>
+  </si>
+  <si>
+    <t>Mahdi</t>
+  </si>
+  <si>
+    <t>Mahdi, Milhane</t>
   </si>
   <si>
     <t>Documentation technique du code Git</t>
@@ -162,12 +177,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Algerian"/>
-      <family val="5"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="9" tint="0.59999389629810485"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -186,6 +195,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Algerian"/>
+      <family val="5"/>
     </font>
   </fonts>
   <fills count="19">
@@ -466,13 +481,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -489,6 +501,34 @@
     <xf numFmtId="14" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -636,8 +676,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -647,13 +687,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -662,19 +702,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -702,6 +742,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -755,12 +798,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>541812</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>173182</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4018280" cy="374141"/>
+    <xdr:ext cx="3268844" cy="374141"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="ZoneTexte 2"/>
@@ -768,8 +811,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15724085" y="912091"/>
-          <a:ext cx="4018280" cy="374141"/>
+          <a:off x="14788903" y="912091"/>
+          <a:ext cx="3268844" cy="374141"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -797,7 +840,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="fr-FR" sz="1800"/>
-            <a:t>Jalon : Soutenance intermédiaire (19/01)</a:t>
+            <a:t>Jalon : Soutenance intermédiaire</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -806,14 +849,14 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>319151</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>353786</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>156427</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>320716</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>355351</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>45357</xdr:rowOff>
     </xdr:to>
@@ -824,8 +867,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="16586696" y="1264791"/>
-          <a:ext cx="1565" cy="258384"/>
+          <a:off x="14459857" y="1244998"/>
+          <a:ext cx="1565" cy="251788"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -850,7 +893,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>197757</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>125187</xdr:rowOff>
@@ -863,7 +906,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25528484" y="864096"/>
+          <a:off x="20399828" y="850901"/>
           <a:ext cx="2548326" cy="374141"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -901,13 +944,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>506265</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>127531</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>709920</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>136471</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>607786</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -916,13 +959,13 @@
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="8" name="Connecteur droit 7"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="7" idx="3"/>
+          <a:stCxn id="7" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28076810" y="1051167"/>
-          <a:ext cx="2341340" cy="426651"/>
+          <a:off x="22435991" y="1225042"/>
+          <a:ext cx="1421866" cy="226387"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1245,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:AA27"/>
+  <dimension ref="B1:AB27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1253,887 +1296,934 @@
     <col min="3" max="3" width="25.81640625" customWidth="1"/>
     <col min="4" max="4" width="12.26953125" customWidth="1"/>
     <col min="5" max="5" width="1.7265625" customWidth="1"/>
-    <col min="6" max="6" width="31.36328125" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="14.6328125" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" customWidth="1"/>
-    <col min="10" max="10" width="2.6328125" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="13" width="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="16" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" customWidth="1"/>
+    <col min="7" max="7" width="24.26953125" customWidth="1"/>
+    <col min="8" max="8" width="23.81640625" customWidth="1"/>
+    <col min="9" max="9" width="14.6328125" customWidth="1"/>
+    <col min="10" max="10" width="15.54296875" customWidth="1"/>
+    <col min="11" max="11" width="2.6328125" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B1" s="91" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="93"/>
-    </row>
-    <row r="2" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="96"/>
-      <c r="F2" s="48" t="s">
+    <row r="1" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B1" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="103"/>
+    </row>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="106"/>
+      <c r="G2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="76"/>
-    </row>
-    <row r="3" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="76"/>
-    </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="F4" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="76"/>
-    </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B5" s="19" t="s">
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="85"/>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="85"/>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="G4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="85"/>
+    </row>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B5" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="20"/>
+      <c r="C5" s="29"/>
       <c r="D5" s="1">
         <v>45999</v>
       </c>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B6" s="19" t="s">
+    <row r="6" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B6" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="1">
         <v>46188</v>
       </c>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="58"/>
-      <c r="X7" s="58"/>
-      <c r="Y7" s="58"/>
-      <c r="Z7" s="58"/>
-    </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="58"/>
-      <c r="V8" s="58"/>
-      <c r="W8" s="58"/>
-      <c r="X8" s="58"/>
-      <c r="Y8" s="58"/>
-      <c r="Z8" s="58"/>
-    </row>
-    <row r="9" spans="2:27" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="77" t="s">
+    <row r="7" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
+      <c r="O7" s="67"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
+      <c r="U7" s="67"/>
+      <c r="V7" s="67"/>
+      <c r="W7" s="67"/>
+      <c r="X7" s="67"/>
+      <c r="Y7" s="67"/>
+      <c r="Z7" s="67"/>
+      <c r="AA7" s="67"/>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="67"/>
+      <c r="O8" s="67"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="67"/>
+      <c r="U8" s="67"/>
+      <c r="V8" s="67"/>
+      <c r="W8" s="67"/>
+      <c r="X8" s="67"/>
+      <c r="Y8" s="67"/>
+      <c r="Z8" s="67"/>
+      <c r="AA8" s="67"/>
+    </row>
+    <row r="9" spans="2:28" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="89" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="100" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="89" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="89"/>
+      <c r="L9" s="90">
+        <v>45999</v>
+      </c>
+      <c r="M9" s="90">
+        <v>46011</v>
+      </c>
+      <c r="N9" s="90">
+        <v>46027</v>
+      </c>
+      <c r="O9" s="90">
+        <v>46037</v>
+      </c>
+      <c r="P9" s="90">
+        <v>46042</v>
+      </c>
+      <c r="Q9" s="90">
+        <v>46048</v>
+      </c>
+      <c r="R9" s="90">
+        <v>46063</v>
+      </c>
+      <c r="S9" s="90">
+        <v>46069</v>
+      </c>
+      <c r="T9" s="90">
+        <v>46090</v>
+      </c>
+      <c r="U9" s="90">
+        <v>46106</v>
+      </c>
+      <c r="V9" s="90">
+        <v>46122</v>
+      </c>
+      <c r="W9" s="90">
+        <v>46132</v>
+      </c>
+      <c r="X9" s="90">
+        <v>46153</v>
+      </c>
+      <c r="Y9" s="90">
+        <v>46162</v>
+      </c>
+      <c r="Z9" s="90">
+        <v>46174</v>
+      </c>
+      <c r="AA9" s="90">
+        <v>46183</v>
+      </c>
+      <c r="AB9" s="90">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="91">
+        <f>SUM(G11:G14)</f>
+        <v>110</v>
+      </c>
+      <c r="H10" s="91">
+        <f>SUM(H11:H14)</f>
+        <v>55</v>
+      </c>
+      <c r="I10" s="5">
+        <v>45999</v>
+      </c>
+      <c r="J10" s="5">
+        <v>46042</v>
+      </c>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="68"/>
+      <c r="Q10" s="69"/>
+      <c r="R10" s="69"/>
+      <c r="S10" s="69"/>
+      <c r="T10" s="69"/>
+      <c r="U10" s="69"/>
+      <c r="V10" s="69"/>
+      <c r="W10" s="69"/>
+      <c r="X10" s="69"/>
+      <c r="Y10" s="69"/>
+      <c r="Z10" s="69"/>
+      <c r="AA10" s="69"/>
+      <c r="AB10" s="66"/>
+    </row>
+    <row r="11" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="92">
+        <v>15</v>
+      </c>
+      <c r="H11" s="92">
+        <v>15</v>
+      </c>
+      <c r="I11" s="72">
+        <v>45999</v>
+      </c>
+      <c r="J11" s="19">
+        <v>46011</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="69"/>
+      <c r="T11" s="69"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="69"/>
+      <c r="W11" s="66"/>
+      <c r="X11" s="66"/>
+      <c r="Y11" s="66"/>
+      <c r="Z11" s="66"/>
+      <c r="AA11" s="66"/>
+      <c r="AB11" s="66"/>
+    </row>
+    <row r="12" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="92">
+        <v>45</v>
+      </c>
+      <c r="H12" s="92">
+        <v>10</v>
+      </c>
+      <c r="I12" s="19">
+        <v>46011</v>
+      </c>
+      <c r="J12" s="19">
+        <v>46027</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="69"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="69"/>
+      <c r="Q12" s="69"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="69"/>
+      <c r="T12" s="69"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="69"/>
+      <c r="W12" s="66"/>
+      <c r="X12" s="66"/>
+      <c r="Y12" s="66"/>
+      <c r="Z12" s="66"/>
+      <c r="AA12" s="66"/>
+      <c r="AB12" s="66"/>
+    </row>
+    <row r="13" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="92">
+        <v>30</v>
+      </c>
+      <c r="H13" s="92">
+        <v>20</v>
+      </c>
+      <c r="I13" s="19">
+        <v>46027</v>
+      </c>
+      <c r="J13" s="19">
+        <v>46037</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="69"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="69"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="69"/>
+      <c r="T13" s="69"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="69"/>
+      <c r="W13" s="66"/>
+      <c r="X13" s="66"/>
+      <c r="Y13" s="66"/>
+      <c r="Z13" s="66"/>
+      <c r="AA13" s="66"/>
+      <c r="AB13" s="66"/>
+    </row>
+    <row r="14" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="92">
+        <v>20</v>
+      </c>
+      <c r="H14" s="92">
+        <v>10</v>
+      </c>
+      <c r="I14" s="19">
+        <v>46032</v>
+      </c>
+      <c r="J14" s="19">
+        <v>46042</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="73"/>
+      <c r="Q14" s="69"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="69"/>
+      <c r="T14" s="69"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="69"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="66"/>
+      <c r="Y14" s="66"/>
+      <c r="Z14" s="66"/>
+      <c r="AA14" s="66"/>
+      <c r="AB14" s="66"/>
+    </row>
+    <row r="15" spans="2:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="93">
+        <f>SUM(G16:G19)</f>
+        <v>85</v>
+      </c>
+      <c r="H15" s="93">
+        <f>SUM(H16:H19)</f>
+        <v>145</v>
+      </c>
+      <c r="I15" s="6">
+        <v>46043</v>
+      </c>
+      <c r="J15" s="6">
+        <v>46132</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="74"/>
+      <c r="T15" s="74"/>
+      <c r="U15" s="74"/>
+      <c r="V15" s="74"/>
+      <c r="W15" s="74"/>
+      <c r="X15" s="69"/>
+      <c r="Y15" s="69"/>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="66"/>
+    </row>
+    <row r="16" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="94">
+        <v>10</v>
+      </c>
+      <c r="H16" s="94">
+        <v>30</v>
+      </c>
+      <c r="I16" s="20">
+        <v>46043</v>
+      </c>
+      <c r="J16" s="20">
+        <v>46063</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="66"/>
+      <c r="M16" s="66"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="76"/>
+      <c r="Q16" s="76"/>
+      <c r="R16" s="76"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="69"/>
+      <c r="W16" s="69"/>
+      <c r="X16" s="69"/>
+      <c r="Y16" s="69"/>
+      <c r="Z16" s="69"/>
+      <c r="AA16" s="69"/>
+      <c r="AB16" s="66"/>
+    </row>
+    <row r="17" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="94">
+        <v>35</v>
+      </c>
+      <c r="H17" s="94">
+        <v>75</v>
+      </c>
+      <c r="I17" s="21">
+        <v>46064</v>
+      </c>
+      <c r="J17" s="75">
+        <v>46106</v>
+      </c>
+      <c r="L17" s="66"/>
+      <c r="M17" s="66"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="66"/>
+      <c r="P17" s="66"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="76"/>
+      <c r="S17" s="76"/>
+      <c r="T17" s="76"/>
+      <c r="U17" s="76"/>
+      <c r="V17" s="69"/>
+      <c r="W17" s="69"/>
+      <c r="X17" s="69"/>
+      <c r="Y17" s="69"/>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="69"/>
+      <c r="AB17" s="66"/>
+    </row>
+    <row r="18" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="94">
+        <v>15</v>
+      </c>
+      <c r="H18" s="94">
+        <v>15</v>
+      </c>
+      <c r="I18" s="20">
+        <v>46107</v>
+      </c>
+      <c r="J18" s="20">
+        <v>46122</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="66"/>
+      <c r="M18" s="66"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="66"/>
+      <c r="P18" s="66"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="66"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="66"/>
+      <c r="U18" s="76"/>
+      <c r="V18" s="76"/>
+      <c r="W18" s="69"/>
+      <c r="X18" s="69"/>
+      <c r="Y18" s="69"/>
+      <c r="Z18" s="69"/>
+      <c r="AA18" s="69"/>
+      <c r="AB18" s="66"/>
+    </row>
+    <row r="19" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="94">
+        <v>25</v>
+      </c>
+      <c r="H19" s="94">
+        <v>25</v>
+      </c>
+      <c r="I19" s="20">
+        <v>46123</v>
+      </c>
+      <c r="J19" s="20">
+        <v>46132</v>
+      </c>
+      <c r="K19" s="2"/>
+      <c r="L19" s="66"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="66"/>
+      <c r="P19" s="66"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="66"/>
+      <c r="S19" s="66"/>
+      <c r="T19" s="66"/>
+      <c r="U19" s="69"/>
+      <c r="V19" s="76"/>
+      <c r="W19" s="76"/>
+      <c r="X19" s="69"/>
+      <c r="Y19" s="69"/>
+      <c r="Z19" s="69"/>
+      <c r="AA19" s="69"/>
+      <c r="AB19" s="66"/>
+    </row>
+    <row r="20" spans="2:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="95">
+        <f>SUM(G21:G22)</f>
+        <v>25</v>
+      </c>
+      <c r="H20" s="95">
+        <f>SUM(H21:H22)</f>
+        <v>35</v>
+      </c>
+      <c r="I20" s="7">
+        <v>46133</v>
+      </c>
+      <c r="J20" s="7">
+        <v>46162</v>
+      </c>
+      <c r="L20" s="66"/>
+      <c r="M20" s="66"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="66"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="66"/>
+      <c r="V20" s="66"/>
+      <c r="W20" s="78"/>
+      <c r="X20" s="70"/>
+      <c r="Y20" s="77"/>
+      <c r="Z20" s="71"/>
+      <c r="AA20" s="71"/>
+      <c r="AB20" s="66"/>
+    </row>
+    <row r="21" spans="2:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="96">
+        <v>15</v>
+      </c>
+      <c r="H21" s="96">
+        <v>25</v>
+      </c>
+      <c r="I21" s="79">
+        <v>46133</v>
+      </c>
+      <c r="J21" s="23">
+        <v>46152</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="66"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="66"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="66"/>
+      <c r="U21" s="66"/>
+      <c r="V21" s="66"/>
+      <c r="W21" s="80"/>
+      <c r="X21" s="80"/>
+      <c r="Y21" s="69"/>
+      <c r="Z21" s="69"/>
+      <c r="AA21" s="69"/>
+      <c r="AB21" s="66"/>
+    </row>
+    <row r="22" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="96">
+        <v>10</v>
+      </c>
+      <c r="H22" s="96">
+        <v>10</v>
+      </c>
+      <c r="I22" s="22">
+        <v>46153</v>
+      </c>
+      <c r="J22" s="22">
+        <v>46162</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="81"/>
+      <c r="Y22" s="81"/>
+      <c r="Z22" s="71"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="66"/>
+    </row>
+    <row r="23" spans="2:28" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="97">
+        <f>SUM(G24:G26)</f>
+        <v>50</v>
+      </c>
+      <c r="H23" s="97">
+        <f>SUM(H24:H26)</f>
+        <v>35</v>
+      </c>
+      <c r="I23" s="8">
+        <v>46163</v>
+      </c>
+      <c r="J23" s="8">
+        <v>46188</v>
+      </c>
+      <c r="L23" s="69"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="69"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="69"/>
+      <c r="T23" s="69"/>
+      <c r="U23" s="69"/>
+      <c r="V23" s="69"/>
+      <c r="W23" s="69"/>
+      <c r="X23" s="69"/>
+      <c r="Y23" s="82"/>
+      <c r="Z23" s="82"/>
+      <c r="AA23" s="82"/>
+      <c r="AB23" s="82"/>
+    </row>
+    <row r="24" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="80" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="80"/>
-      <c r="K9" s="81">
-        <v>45999</v>
-      </c>
-      <c r="L9" s="81">
-        <v>46011</v>
-      </c>
-      <c r="M9" s="81">
-        <v>46027</v>
-      </c>
-      <c r="N9" s="81">
-        <v>46037</v>
-      </c>
-      <c r="O9" s="81">
-        <v>46042</v>
-      </c>
-      <c r="P9" s="81">
-        <v>46048</v>
-      </c>
-      <c r="Q9" s="81">
-        <v>46063</v>
-      </c>
-      <c r="R9" s="81">
-        <v>46069</v>
-      </c>
-      <c r="S9" s="81">
-        <v>46090</v>
-      </c>
-      <c r="T9" s="81">
-        <v>46106</v>
-      </c>
-      <c r="U9" s="81">
-        <v>46122</v>
-      </c>
-      <c r="V9" s="81">
-        <v>46132</v>
-      </c>
-      <c r="W9" s="81">
-        <v>46153</v>
-      </c>
-      <c r="X9" s="81">
-        <v>46162</v>
-      </c>
-      <c r="Y9" s="81">
+      <c r="G24" s="98">
+        <v>10</v>
+      </c>
+      <c r="H24" s="98">
+        <v>20</v>
+      </c>
+      <c r="I24" s="83">
+        <v>46163</v>
+      </c>
+      <c r="J24" s="24">
         <v>46174</v>
       </c>
-      <c r="Z9" s="81">
+      <c r="K24" s="2"/>
+      <c r="L24" s="69"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69"/>
+      <c r="U24" s="69"/>
+      <c r="V24" s="69"/>
+      <c r="W24" s="69"/>
+      <c r="X24" s="69"/>
+      <c r="Y24" s="84"/>
+      <c r="Z24" s="84"/>
+      <c r="AA24" s="69"/>
+      <c r="AB24" s="66"/>
+    </row>
+    <row r="25" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="98">
+        <v>35</v>
+      </c>
+      <c r="H25" s="98">
+        <v>10</v>
+      </c>
+      <c r="I25" s="24">
+        <v>46174</v>
+      </c>
+      <c r="J25" s="24">
         <v>46183</v>
       </c>
-      <c r="AA9" s="81">
+      <c r="L25" s="69"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="69"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="69"/>
+      <c r="U25" s="69"/>
+      <c r="V25" s="69"/>
+      <c r="W25" s="69"/>
+      <c r="X25" s="69"/>
+      <c r="Y25" s="69"/>
+      <c r="Z25" s="84"/>
+      <c r="AA25" s="84"/>
+      <c r="AB25" s="66"/>
+    </row>
+    <row r="26" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="98">
+        <v>5</v>
+      </c>
+      <c r="H26" s="98">
+        <v>5</v>
+      </c>
+      <c r="I26" s="24">
+        <v>46183</v>
+      </c>
+      <c r="J26" s="24">
         <v>46188</v>
       </c>
-    </row>
-    <row r="10" spans="2:27" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="82">
-        <f>SUM(F11:F14)</f>
-        <v>110</v>
-      </c>
-      <c r="G10" s="82">
-        <f>SUM(G11:G14)</f>
-        <v>55</v>
-      </c>
-      <c r="H10" s="6">
-        <v>45999</v>
-      </c>
-      <c r="I10" s="6">
-        <v>46042</v>
-      </c>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="59"/>
-      <c r="N10" s="59"/>
-      <c r="O10" s="59"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="60"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="60"/>
-      <c r="U10" s="60"/>
-      <c r="V10" s="60"/>
-      <c r="W10" s="60"/>
-      <c r="X10" s="60"/>
-      <c r="Y10" s="60"/>
-      <c r="Z10" s="60"/>
-      <c r="AA10" s="57"/>
-    </row>
-    <row r="11" spans="2:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="83">
-        <v>15</v>
-      </c>
-      <c r="G11" s="83">
-        <v>15</v>
-      </c>
-      <c r="H11" s="63">
-        <v>45999</v>
-      </c>
-      <c r="I11" s="10">
-        <v>46011</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="60"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="60"/>
-      <c r="U11" s="60"/>
-      <c r="V11" s="57"/>
-      <c r="W11" s="57"/>
-      <c r="X11" s="57"/>
-      <c r="Y11" s="57"/>
-      <c r="Z11" s="57"/>
-      <c r="AA11" s="57"/>
-    </row>
-    <row r="12" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="83">
-        <v>45</v>
-      </c>
-      <c r="G12" s="83">
-        <v>10</v>
-      </c>
-      <c r="H12" s="10">
-        <v>46011</v>
-      </c>
-      <c r="I12" s="10">
-        <v>46027</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="60"/>
-      <c r="O12" s="60"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="60"/>
-      <c r="T12" s="60"/>
-      <c r="U12" s="60"/>
-      <c r="V12" s="57"/>
-      <c r="W12" s="57"/>
-      <c r="X12" s="57"/>
-      <c r="Y12" s="57"/>
-      <c r="Z12" s="57"/>
-      <c r="AA12" s="57"/>
-    </row>
-    <row r="13" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="83">
-        <v>30</v>
-      </c>
-      <c r="G13" s="83">
-        <v>20</v>
-      </c>
-      <c r="H13" s="10">
-        <v>46027</v>
-      </c>
-      <c r="I13" s="10">
-        <v>46037</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="64"/>
-      <c r="O13" s="64"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="57"/>
-      <c r="W13" s="57"/>
-      <c r="X13" s="57"/>
-      <c r="Y13" s="57"/>
-      <c r="Z13" s="57"/>
-      <c r="AA13" s="57"/>
-    </row>
-    <row r="14" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="83">
-        <v>20</v>
-      </c>
-      <c r="G14" s="83">
-        <v>10</v>
-      </c>
-      <c r="H14" s="10">
-        <v>46032</v>
-      </c>
-      <c r="I14" s="10">
-        <v>46042</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="64"/>
-      <c r="N14" s="64"/>
-      <c r="O14" s="64"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="60"/>
-      <c r="T14" s="60"/>
-      <c r="U14" s="60"/>
-      <c r="V14" s="57"/>
-      <c r="W14" s="57"/>
-      <c r="X14" s="57"/>
-      <c r="Y14" s="57"/>
-      <c r="Z14" s="57"/>
-      <c r="AA14" s="57"/>
-    </row>
-    <row r="15" spans="2:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="84">
-        <f>SUM(F16:F19)</f>
-        <v>85</v>
-      </c>
-      <c r="G15" s="84">
-        <f>SUM(G16:G19)</f>
-        <v>145</v>
-      </c>
-      <c r="H15" s="7">
-        <v>46043</v>
-      </c>
-      <c r="I15" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="65"/>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="65"/>
-      <c r="S15" s="65"/>
-      <c r="T15" s="65"/>
-      <c r="U15" s="65"/>
-      <c r="V15" s="65"/>
-      <c r="W15" s="60"/>
-      <c r="X15" s="60"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="60"/>
-      <c r="AA15" s="57"/>
-    </row>
-    <row r="16" spans="2:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="85">
-        <v>10</v>
-      </c>
-      <c r="G16" s="85">
-        <v>30</v>
-      </c>
-      <c r="H16" s="11">
-        <v>46043</v>
-      </c>
-      <c r="I16" s="11">
-        <v>46063</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="57"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="67"/>
-      <c r="Q16" s="67"/>
-      <c r="R16" s="57"/>
-      <c r="S16" s="57"/>
-      <c r="T16" s="60"/>
-      <c r="U16" s="60"/>
-      <c r="V16" s="60"/>
-      <c r="W16" s="60"/>
-      <c r="X16" s="60"/>
-      <c r="Y16" s="60"/>
-      <c r="Z16" s="60"/>
-      <c r="AA16" s="57"/>
-    </row>
-    <row r="17" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="85">
-        <v>35</v>
-      </c>
-      <c r="G17" s="85">
-        <v>75</v>
-      </c>
-      <c r="H17" s="12">
-        <v>46064</v>
-      </c>
-      <c r="I17" s="66">
-        <v>46106</v>
-      </c>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="57"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="57"/>
-      <c r="P17" s="57"/>
-      <c r="Q17" s="67"/>
-      <c r="R17" s="67"/>
-      <c r="S17" s="67"/>
-      <c r="T17" s="67"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="60"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
-      <c r="Z17" s="60"/>
-      <c r="AA17" s="57"/>
-    </row>
-    <row r="18" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="85">
-        <v>15</v>
-      </c>
-      <c r="G18" s="85">
-        <v>15</v>
-      </c>
-      <c r="H18" s="11">
-        <v>46107</v>
-      </c>
-      <c r="I18" s="11">
-        <v>46122</v>
-      </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="57"/>
-      <c r="R18" s="57"/>
-      <c r="S18" s="57"/>
-      <c r="T18" s="67"/>
-      <c r="U18" s="67"/>
-      <c r="V18" s="60"/>
-      <c r="W18" s="60"/>
-      <c r="X18" s="60"/>
-      <c r="Y18" s="60"/>
-      <c r="Z18" s="60"/>
-      <c r="AA18" s="57"/>
-    </row>
-    <row r="19" spans="2:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="85">
-        <v>25</v>
-      </c>
-      <c r="G19" s="85">
-        <v>25</v>
-      </c>
-      <c r="H19" s="11">
-        <v>46123</v>
-      </c>
-      <c r="I19" s="11">
-        <v>46132</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="60"/>
-      <c r="U19" s="67"/>
-      <c r="V19" s="67"/>
-      <c r="W19" s="60"/>
-      <c r="X19" s="60"/>
-      <c r="Y19" s="60"/>
-      <c r="Z19" s="60"/>
-      <c r="AA19" s="57"/>
-    </row>
-    <row r="20" spans="2:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="86">
-        <f>SUM(F21:F22)</f>
-        <v>25</v>
-      </c>
-      <c r="G20" s="86">
-        <f>SUM(G21:G22)</f>
-        <v>35</v>
-      </c>
-      <c r="H20" s="8">
-        <v>46133</v>
-      </c>
-      <c r="I20" s="8">
-        <v>46162</v>
-      </c>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="57"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="57"/>
-      <c r="S20" s="57"/>
-      <c r="T20" s="57"/>
-      <c r="U20" s="57"/>
-      <c r="V20" s="69"/>
-      <c r="W20" s="61"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="62"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="57"/>
-    </row>
-    <row r="21" spans="2:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="87">
-        <v>15</v>
-      </c>
-      <c r="G21" s="87">
-        <v>25</v>
-      </c>
-      <c r="H21" s="70">
-        <v>46133</v>
-      </c>
-      <c r="I21" s="14">
-        <v>46152</v>
-      </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="57"/>
-      <c r="P21" s="57"/>
-      <c r="Q21" s="57"/>
-      <c r="R21" s="57"/>
-      <c r="S21" s="57"/>
-      <c r="T21" s="57"/>
-      <c r="U21" s="57"/>
-      <c r="V21" s="71"/>
-      <c r="W21" s="71"/>
-      <c r="X21" s="60"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="60"/>
-      <c r="AA21" s="57"/>
-    </row>
-    <row r="22" spans="2:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="87">
-        <v>10</v>
-      </c>
-      <c r="G22" s="87">
-        <v>10</v>
-      </c>
-      <c r="H22" s="13">
-        <v>46153</v>
-      </c>
-      <c r="I22" s="13">
-        <v>46162</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="57"/>
-      <c r="P22" s="57"/>
-      <c r="Q22" s="57"/>
-      <c r="R22" s="57"/>
-      <c r="S22" s="57"/>
-      <c r="T22" s="57"/>
-      <c r="U22" s="57"/>
-      <c r="V22" s="57"/>
-      <c r="W22" s="72"/>
-      <c r="X22" s="72"/>
-      <c r="Y22" s="62"/>
-      <c r="Z22" s="62"/>
-      <c r="AA22" s="57"/>
-    </row>
-    <row r="23" spans="2:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="88">
-        <f>SUM(F24:F26)</f>
-        <v>50</v>
-      </c>
-      <c r="G23" s="88">
-        <f>SUM(G24:G26)</f>
-        <v>35</v>
-      </c>
-      <c r="H23" s="9">
-        <v>46163</v>
-      </c>
-      <c r="I23" s="9">
-        <v>46188</v>
-      </c>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="60"/>
-      <c r="T23" s="60"/>
-      <c r="U23" s="60"/>
-      <c r="V23" s="60"/>
-      <c r="W23" s="60"/>
-      <c r="X23" s="73"/>
-      <c r="Y23" s="73"/>
-      <c r="Z23" s="73"/>
-      <c r="AA23" s="73"/>
-    </row>
-    <row r="24" spans="2:27" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="89">
-        <v>10</v>
-      </c>
-      <c r="G24" s="89">
-        <v>20</v>
-      </c>
-      <c r="H24" s="74">
-        <v>46163</v>
-      </c>
-      <c r="I24" s="15">
-        <v>46174</v>
-      </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="60"/>
-      <c r="M24" s="60"/>
-      <c r="N24" s="60"/>
-      <c r="O24" s="60"/>
-      <c r="P24" s="60"/>
-      <c r="Q24" s="60"/>
-      <c r="R24" s="60"/>
-      <c r="S24" s="60"/>
-      <c r="T24" s="60"/>
-      <c r="U24" s="60"/>
-      <c r="V24" s="60"/>
-      <c r="W24" s="60"/>
-      <c r="X24" s="75"/>
-      <c r="Y24" s="75"/>
-      <c r="Z24" s="60"/>
-      <c r="AA24" s="57"/>
-    </row>
-    <row r="25" spans="2:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="89">
-        <v>35</v>
-      </c>
-      <c r="G25" s="89">
-        <v>10</v>
-      </c>
-      <c r="H25" s="15">
-        <v>46174</v>
-      </c>
-      <c r="I25" s="15">
-        <v>46183</v>
-      </c>
-      <c r="K25" s="60"/>
-      <c r="L25" s="60"/>
-      <c r="M25" s="60"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="60"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="60"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="60"/>
-      <c r="U25" s="60"/>
-      <c r="V25" s="60"/>
-      <c r="W25" s="60"/>
-      <c r="X25" s="60"/>
-      <c r="Y25" s="75"/>
-      <c r="Z25" s="75"/>
-      <c r="AA25" s="57"/>
-    </row>
-    <row r="26" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="89">
-        <v>5</v>
-      </c>
-      <c r="G26" s="89">
-        <v>5</v>
-      </c>
-      <c r="H26" s="15">
-        <v>46183</v>
-      </c>
-      <c r="I26" s="15">
-        <v>46188</v>
-      </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="60"/>
-      <c r="M26" s="60"/>
-      <c r="N26" s="60"/>
-      <c r="O26" s="60"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="60"/>
-      <c r="R26" s="60"/>
-      <c r="S26" s="60"/>
-      <c r="T26" s="60"/>
-      <c r="U26" s="60"/>
-      <c r="V26" s="60"/>
-      <c r="W26" s="60"/>
-      <c r="X26" s="60"/>
-      <c r="Y26" s="60"/>
-      <c r="Z26" s="75"/>
-      <c r="AA26" s="75"/>
-    </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="F27" s="90">
-        <f>SUM(F23,F20,F15,F10)</f>
-        <v>270</v>
-      </c>
-      <c r="G27" s="90">
+      <c r="K26" s="2"/>
+      <c r="L26" s="69"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="69"/>
+      <c r="O26" s="69"/>
+      <c r="P26" s="69"/>
+      <c r="Q26" s="69"/>
+      <c r="R26" s="69"/>
+      <c r="S26" s="69"/>
+      <c r="T26" s="69"/>
+      <c r="U26" s="69"/>
+      <c r="V26" s="69"/>
+      <c r="W26" s="69"/>
+      <c r="X26" s="69"/>
+      <c r="Y26" s="69"/>
+      <c r="Z26" s="69"/>
+      <c r="AA26" s="84"/>
+      <c r="AB26" s="84"/>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="G27" s="99">
         <f>SUM(G23,G20,G15,G10)</f>
         <v>270</v>
       </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="5"/>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5"/>
-      <c r="Z27" s="5"/>
+      <c r="H27" s="99">
+        <f>SUM(H23,H20,H15,H10)</f>
+        <v>270</v>
+      </c>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F2:P3"/>
-    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="G2:Q3"/>
+    <mergeCell ref="G4:Q4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B11:E11"/>

--- a/Gantt.xlsx
+++ b/Gantt.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jojo\Documents\TER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milha\OneDrive\Documents\JADE\abstrats\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BDACCD-123E-4EA6-9C09-469817D6080B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7020"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,14 +27,19 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
   <si>
     <t>Diagramme de gantt</t>
   </si>
@@ -129,13 +135,49 @@
   </si>
   <si>
     <t xml:space="preserve">     Tâche</t>
+  </si>
+  <si>
+    <t>Securisation et configuration centralisée</t>
+  </si>
+  <si>
+    <t>Externalsiation et optimisation SQL</t>
+  </si>
+  <si>
+    <t>Création de couches analytique (Vues)</t>
+  </si>
+  <si>
+    <t>Refactorisation et programmation orientée objet (POO)</t>
+  </si>
+  <si>
+    <t>Orchestration du pipeline ETL</t>
+  </si>
+  <si>
+    <t>Conteneurisation de l'application (Docker)</t>
+  </si>
+  <si>
+    <t>Mise en place des tests unitaires automatisées</t>
+  </si>
+  <si>
+    <t>Systèmes d'audit et de journalisation</t>
+  </si>
+  <si>
+    <t>Analytiques &amp; Data science</t>
+  </si>
+  <si>
+    <t>Développement du dashboard interactif</t>
+  </si>
+  <si>
+    <t>Modélisation statistique et Machine learning</t>
+  </si>
+  <si>
+    <t>Configuration de l'environnement de développement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,8 +244,15 @@
       <name val="Algerian"/>
       <family val="5"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,6 +358,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -481,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -546,129 +607,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -702,15 +640,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -735,9 +664,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -747,6 +673,154 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -764,6 +838,48 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,12 +890,12 @@
   <colors>
     <mruColors>
       <color rgb="FFFCE4D6"/>
+      <color rgb="FFBDD7EE"/>
+      <color rgb="FFFFF2CC"/>
       <color rgb="FFF8CBAD"/>
       <color rgb="FFE2EFDA"/>
       <color rgb="FFC6E0B4"/>
       <color rgb="FFDDEBF7"/>
-      <color rgb="FFBDD7EE"/>
-      <color rgb="FFFFF2CC"/>
       <color rgb="FF4E4C00"/>
     </mruColors>
   </colors>
@@ -806,7 +922,13 @@
     <xdr:ext cx="3268844" cy="374141"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="ZoneTexte 2"/>
+        <xdr:cNvPr id="3" name="ZoneTexte 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -862,7 +984,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="Connecteur droit 4"/>
+        <xdr:cNvPr id="5" name="Connecteur droit 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -901,7 +1029,13 @@
     <xdr:ext cx="2548326" cy="374141"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="ZoneTexte 6"/>
+        <xdr:cNvPr id="7" name="ZoneTexte 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -957,7 +1091,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="Connecteur droit 7"/>
+        <xdr:cNvPr id="8" name="Connecteur droit 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="2"/>
         </xdr:cNvCxnSpPr>
@@ -1287,314 +1427,314 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:AB27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:AB39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="17.26953125" customWidth="1"/>
-    <col min="3" max="3" width="25.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" customWidth="1"/>
-    <col min="5" max="5" width="1.7265625" customWidth="1"/>
-    <col min="6" max="6" width="15.90625" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" customWidth="1"/>
-    <col min="8" max="8" width="23.81640625" customWidth="1"/>
-    <col min="9" max="9" width="14.6328125" customWidth="1"/>
-    <col min="10" max="10" width="15.54296875" customWidth="1"/>
-    <col min="11" max="11" width="2.6328125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" customWidth="1"/>
+    <col min="8" max="8" width="23.85546875" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
     <col min="13" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="19" width="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="26" max="28" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B1" s="101" t="s">
+    <row r="1" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B1" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="103"/>
-    </row>
-    <row r="2" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B2" s="104"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="106"/>
-      <c r="G2" s="57" t="s">
+      <c r="C1" s="111"/>
+      <c r="D1" s="112"/>
+    </row>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B2" s="113"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="115"/>
+      <c r="G2" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="85"/>
-    </row>
-    <row r="3" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="G3" s="54"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="85"/>
-    </row>
-    <row r="4" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="G4" s="60" t="s">
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="44"/>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="G3" s="119"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="120"/>
+      <c r="O3" s="120"/>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="44"/>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="G4" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="85"/>
-    </row>
-    <row r="5" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="44"/>
+    </row>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B5" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="29"/>
+      <c r="C5" s="126"/>
       <c r="D5" s="1">
         <v>45999</v>
       </c>
     </row>
-    <row r="6" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B6" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="126"/>
       <c r="D6" s="1">
         <v>46188</v>
       </c>
     </row>
-    <row r="7" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="67"/>
-      <c r="O7" s="67"/>
-      <c r="P7" s="67"/>
-      <c r="Q7" s="67"/>
-      <c r="R7" s="67"/>
-      <c r="S7" s="67"/>
-      <c r="T7" s="67"/>
-      <c r="U7" s="67"/>
-      <c r="V7" s="67"/>
-      <c r="W7" s="67"/>
-      <c r="X7" s="67"/>
-      <c r="Y7" s="67"/>
-      <c r="Z7" s="67"/>
-      <c r="AA7" s="67"/>
-    </row>
-    <row r="8" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="67"/>
-      <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="67"/>
-      <c r="T8" s="67"/>
-      <c r="U8" s="67"/>
-      <c r="V8" s="67"/>
-      <c r="W8" s="67"/>
-      <c r="X8" s="67"/>
-      <c r="Y8" s="67"/>
-      <c r="Z8" s="67"/>
-      <c r="AA8" s="67"/>
-    </row>
-    <row r="9" spans="2:28" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="86" t="s">
+    <row r="7" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="26"/>
+      <c r="U7" s="26"/>
+      <c r="V7" s="26"/>
+      <c r="W7" s="26"/>
+      <c r="X7" s="26"/>
+      <c r="Y7" s="26"/>
+      <c r="Z7" s="26"/>
+      <c r="AA7" s="26"/>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="26"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="26"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="26"/>
+    </row>
+    <row r="9" spans="2:28" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="89" t="s">
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="109"/>
+      <c r="F9" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="100" t="s">
+      <c r="G9" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="100" t="s">
+      <c r="H9" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="89" t="s">
+      <c r="I9" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="J9" s="89" t="s">
+      <c r="J9" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="89"/>
-      <c r="L9" s="90">
+      <c r="K9" s="45"/>
+      <c r="L9" s="46">
         <v>45999</v>
       </c>
-      <c r="M9" s="90">
+      <c r="M9" s="46">
         <v>46011</v>
       </c>
-      <c r="N9" s="90">
+      <c r="N9" s="46">
         <v>46027</v>
       </c>
-      <c r="O9" s="90">
+      <c r="O9" s="46">
         <v>46037</v>
       </c>
-      <c r="P9" s="90">
+      <c r="P9" s="46">
         <v>46042</v>
       </c>
-      <c r="Q9" s="90">
+      <c r="Q9" s="46">
         <v>46048</v>
       </c>
-      <c r="R9" s="90">
+      <c r="R9" s="46">
         <v>46063</v>
       </c>
-      <c r="S9" s="90">
+      <c r="S9" s="46">
         <v>46069</v>
       </c>
-      <c r="T9" s="90">
+      <c r="T9" s="46">
         <v>46090</v>
       </c>
-      <c r="U9" s="90">
+      <c r="U9" s="46">
         <v>46106</v>
       </c>
-      <c r="V9" s="90">
+      <c r="V9" s="46">
         <v>46122</v>
       </c>
-      <c r="W9" s="90">
+      <c r="W9" s="46">
         <v>46132</v>
       </c>
-      <c r="X9" s="90">
+      <c r="X9" s="46">
         <v>46153</v>
       </c>
-      <c r="Y9" s="90">
+      <c r="Y9" s="46">
         <v>46162</v>
       </c>
-      <c r="Z9" s="90">
+      <c r="Z9" s="46">
         <v>46174</v>
       </c>
-      <c r="AA9" s="90">
+      <c r="AA9" s="46">
         <v>46183</v>
       </c>
-      <c r="AB9" s="90">
+      <c r="AB9" s="46">
         <v>46188</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="63" t="s">
+    <row r="10" spans="2:28" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="65"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="106"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="91">
-        <f>SUM(G11:G14)</f>
-        <v>110</v>
-      </c>
-      <c r="H10" s="91">
-        <f>SUM(H11:H14)</f>
-        <v>55</v>
+      <c r="G10" s="47">
+        <f>SUM(G11:G16)</f>
+        <v>100</v>
+      </c>
+      <c r="H10" s="47">
+        <f>SUM(H11:H16)</f>
+        <v>35</v>
       </c>
       <c r="I10" s="5">
         <v>45999</v>
       </c>
       <c r="J10" s="5">
-        <v>46042</v>
-      </c>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="68"/>
-      <c r="P10" s="68"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="69"/>
-      <c r="AA10" s="69"/>
-      <c r="AB10" s="66"/>
-    </row>
-    <row r="11" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="51" t="s">
+        <v>46142</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="28"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="25"/>
+    </row>
+    <row r="11" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="53"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="100"/>
       <c r="F11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="92">
+      <c r="G11" s="48">
         <v>15</v>
       </c>
-      <c r="H11" s="92">
-        <v>15</v>
-      </c>
-      <c r="I11" s="72">
+      <c r="H11" s="48">
+        <v>5</v>
+      </c>
+      <c r="I11" s="31">
         <v>45999</v>
       </c>
       <c r="J11" s="19">
         <v>46011</v>
       </c>
       <c r="K11" s="2"/>
-      <c r="L11" s="73"/>
-      <c r="M11" s="73"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="69"/>
-      <c r="R11" s="69"/>
-      <c r="S11" s="69"/>
-      <c r="T11" s="69"/>
-      <c r="U11" s="69"/>
-      <c r="V11" s="69"/>
-      <c r="W11" s="66"/>
-      <c r="X11" s="66"/>
-      <c r="Y11" s="66"/>
-      <c r="Z11" s="66"/>
-      <c r="AA11" s="66"/>
-      <c r="AB11" s="66"/>
-    </row>
-    <row r="12" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="51" t="s">
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+    </row>
+    <row r="12" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="53"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="100"/>
       <c r="F12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="92">
-        <v>45</v>
-      </c>
-      <c r="H12" s="92">
-        <v>10</v>
+      <c r="G12" s="48">
+        <v>35</v>
+      </c>
+      <c r="H12" s="48">
+        <v>5</v>
       </c>
       <c r="I12" s="19">
         <v>46011</v>
@@ -1603,39 +1743,39 @@
         <v>46027</v>
       </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="73"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="69"/>
-      <c r="R12" s="69"/>
-      <c r="S12" s="69"/>
-      <c r="T12" s="69"/>
-      <c r="U12" s="69"/>
-      <c r="V12" s="69"/>
-      <c r="W12" s="66"/>
-      <c r="X12" s="66"/>
-      <c r="Y12" s="66"/>
-      <c r="Z12" s="66"/>
-      <c r="AA12" s="66"/>
-      <c r="AB12" s="66"/>
-    </row>
-    <row r="13" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="51" t="s">
+      <c r="L12" s="28"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+    </row>
+    <row r="13" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="53"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="100"/>
       <c r="F13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="92">
-        <v>30</v>
-      </c>
-      <c r="H13" s="92">
-        <v>20</v>
+      <c r="G13" s="48">
+        <v>15</v>
+      </c>
+      <c r="H13" s="48">
+        <v>10</v>
       </c>
       <c r="I13" s="19">
         <v>46027</v>
@@ -1644,39 +1784,39 @@
         <v>46037</v>
       </c>
       <c r="K13" s="2"/>
-      <c r="L13" s="69"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="73"/>
-      <c r="O13" s="73"/>
-      <c r="P13" s="73"/>
-      <c r="Q13" s="69"/>
-      <c r="R13" s="69"/>
-      <c r="S13" s="69"/>
-      <c r="T13" s="69"/>
-      <c r="U13" s="69"/>
-      <c r="V13" s="69"/>
-      <c r="W13" s="66"/>
-      <c r="X13" s="66"/>
-      <c r="Y13" s="66"/>
-      <c r="Z13" s="66"/>
-      <c r="AA13" s="66"/>
-      <c r="AB13" s="66"/>
-    </row>
-    <row r="14" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="51" t="s">
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+    </row>
+    <row r="14" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="53"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="100"/>
       <c r="F14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="92">
-        <v>20</v>
-      </c>
-      <c r="H14" s="92">
+      <c r="G14" s="48">
         <v>10</v>
+      </c>
+      <c r="H14" s="48">
+        <v>5</v>
       </c>
       <c r="I14" s="19">
         <v>46032</v>
@@ -1685,540 +1825,1035 @@
         <v>46042</v>
       </c>
       <c r="K14" s="2"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="69"/>
-      <c r="R14" s="69"/>
-      <c r="S14" s="69"/>
-      <c r="T14" s="69"/>
-      <c r="U14" s="69"/>
-      <c r="V14" s="69"/>
-      <c r="W14" s="66"/>
-      <c r="X14" s="66"/>
-      <c r="Y14" s="66"/>
-      <c r="Z14" s="66"/>
-      <c r="AA14" s="66"/>
-      <c r="AB14" s="66"/>
-    </row>
-    <row r="15" spans="2:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="30" t="s">
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="28"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+    </row>
+    <row r="15" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="98" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="48">
+        <v>10</v>
+      </c>
+      <c r="H15" s="48">
+        <v>0</v>
+      </c>
+      <c r="I15" s="19">
+        <v>46027</v>
+      </c>
+      <c r="J15" s="19">
+        <v>46142</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="61"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="61"/>
+      <c r="T15" s="61"/>
+      <c r="U15" s="61"/>
+      <c r="V15" s="61"/>
+      <c r="W15" s="61"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+    </row>
+    <row r="16" spans="2:28" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="98" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="99"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="48">
         <v>15</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="93">
-        <f>SUM(G16:G19)</f>
-        <v>85</v>
-      </c>
-      <c r="H15" s="93">
-        <f>SUM(H16:H19)</f>
-        <v>145</v>
-      </c>
-      <c r="I15" s="6">
+      <c r="H16" s="48">
+        <v>10</v>
+      </c>
+      <c r="I16" s="19">
+        <v>46054</v>
+      </c>
+      <c r="J16" s="19">
+        <v>46082</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="61"/>
+      <c r="S16" s="61"/>
+      <c r="T16" s="61"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+    </row>
+    <row r="17" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="48">
+        <v>15</v>
+      </c>
+      <c r="H17" s="62">
+        <v>0</v>
+      </c>
+      <c r="I17" s="19">
+        <v>46096</v>
+      </c>
+      <c r="J17" s="60">
+        <v>46142</v>
+      </c>
+      <c r="K17" s="2"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="61"/>
+      <c r="W17" s="61"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+    </row>
+    <row r="18" spans="2:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="49">
+        <f>SUM(G19:G24)</f>
+        <v>90</v>
+      </c>
+      <c r="H18" s="49">
+        <f>SUM(H19:H24)</f>
+        <v>150</v>
+      </c>
+      <c r="I18" s="6">
         <v>46043</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J18" s="6">
+        <v>46173</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="28"/>
+      <c r="AA18" s="28"/>
+      <c r="AB18" s="25"/>
+    </row>
+    <row r="19" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="50">
+        <v>10</v>
+      </c>
+      <c r="H19" s="50">
+        <v>30</v>
+      </c>
+      <c r="I19" s="20">
+        <v>46043</v>
+      </c>
+      <c r="J19" s="20">
+        <v>46063</v>
+      </c>
+      <c r="K19" s="2"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="25"/>
+    </row>
+    <row r="20" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="50">
+        <v>15</v>
+      </c>
+      <c r="H20" s="50">
+        <v>55</v>
+      </c>
+      <c r="I20" s="21">
+        <v>46064</v>
+      </c>
+      <c r="J20" s="34">
+        <v>46106</v>
+      </c>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="25"/>
+    </row>
+    <row r="21" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="89" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="90"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="50">
+        <v>15</v>
+      </c>
+      <c r="H21" s="50">
+        <v>15</v>
+      </c>
+      <c r="I21" s="20">
+        <v>46107</v>
+      </c>
+      <c r="J21" s="20">
+        <v>46122</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="28"/>
+      <c r="X21" s="28"/>
+      <c r="Y21" s="28"/>
+      <c r="Z21" s="28"/>
+      <c r="AA21" s="28"/>
+      <c r="AB21" s="25"/>
+    </row>
+    <row r="22" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="50">
+        <v>15</v>
+      </c>
+      <c r="H22" s="50">
+        <v>25</v>
+      </c>
+      <c r="I22" s="20">
+        <v>46123</v>
+      </c>
+      <c r="J22" s="20">
         <v>46132</v>
       </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="69"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="74"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="74"/>
-      <c r="S15" s="74"/>
-      <c r="T15" s="74"/>
-      <c r="U15" s="74"/>
-      <c r="V15" s="74"/>
-      <c r="W15" s="74"/>
-      <c r="X15" s="69"/>
-      <c r="Y15" s="69"/>
-      <c r="Z15" s="69"/>
-      <c r="AA15" s="69"/>
-      <c r="AB15" s="66"/>
-    </row>
-    <row r="16" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="12" t="s">
+      <c r="K22" s="2"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="28"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="28"/>
+      <c r="AA22" s="28"/>
+      <c r="AB22" s="25"/>
+    </row>
+    <row r="23" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="50">
+        <v>20</v>
+      </c>
+      <c r="H23" s="50">
+        <v>25</v>
+      </c>
+      <c r="I23" s="20">
+        <v>46143</v>
+      </c>
+      <c r="J23" s="20">
+        <v>46167</v>
+      </c>
+      <c r="K23" s="2"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="72"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="28"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="25"/>
+    </row>
+    <row r="24" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="89" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="50">
+        <v>15</v>
+      </c>
+      <c r="H24" s="50">
+        <v>0</v>
+      </c>
+      <c r="I24" s="20">
+        <v>46149</v>
+      </c>
+      <c r="J24" s="20">
+        <v>46167</v>
+      </c>
+      <c r="K24" s="2"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="72"/>
+      <c r="X24" s="72"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="28"/>
+      <c r="AA24" s="28"/>
+      <c r="AB24" s="25"/>
+    </row>
+    <row r="25" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="95" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="96"/>
+      <c r="D25" s="96"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="94">
+      <c r="G25" s="63">
+        <v>0</v>
+      </c>
+      <c r="H25" s="63">
+        <v>15</v>
+      </c>
+      <c r="I25" s="20">
+        <v>46157</v>
+      </c>
+      <c r="J25" s="20">
+        <v>46173</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="72"/>
+      <c r="X25" s="72"/>
+      <c r="Y25" s="72"/>
+      <c r="Z25" s="28"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="25"/>
+    </row>
+    <row r="26" spans="2:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="51">
+        <f>SUM(G27:G29)</f>
+        <v>15</v>
+      </c>
+      <c r="H26" s="51">
+        <f>SUM(H27:H29)</f>
+        <v>35</v>
+      </c>
+      <c r="I26" s="7">
+        <v>46133</v>
+      </c>
+      <c r="J26" s="7">
+        <v>46173</v>
+      </c>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="36"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="25"/>
+    </row>
+    <row r="27" spans="2:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="52">
+        <v>5</v>
+      </c>
+      <c r="H27" s="52">
+        <v>15</v>
+      </c>
+      <c r="I27" s="38">
+        <v>46133</v>
+      </c>
+      <c r="J27" s="23">
+        <v>46152</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
+      <c r="W27" s="39"/>
+      <c r="X27" s="39"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="25"/>
+    </row>
+    <row r="28" spans="2:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="52">
         <v>10</v>
       </c>
-      <c r="H16" s="94">
-        <v>30</v>
-      </c>
-      <c r="I16" s="20">
-        <v>46043</v>
-      </c>
-      <c r="J16" s="20">
-        <v>46063</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="66"/>
-      <c r="M16" s="66"/>
-      <c r="N16" s="66"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="76"/>
-      <c r="Q16" s="76"/>
-      <c r="R16" s="76"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="69"/>
-      <c r="V16" s="69"/>
-      <c r="W16" s="69"/>
-      <c r="X16" s="69"/>
-      <c r="Y16" s="69"/>
-      <c r="Z16" s="69"/>
-      <c r="AA16" s="69"/>
-      <c r="AB16" s="66"/>
-    </row>
-    <row r="17" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="13" t="s">
+      <c r="H28" s="52">
+        <v>10</v>
+      </c>
+      <c r="I28" s="22">
+        <v>46153</v>
+      </c>
+      <c r="J28" s="22">
+        <v>46162</v>
+      </c>
+      <c r="K28" s="2"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="25"/>
+    </row>
+    <row r="29" spans="2:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="52">
+        <v>0</v>
+      </c>
+      <c r="H29" s="52">
+        <v>10</v>
+      </c>
+      <c r="I29" s="38">
+        <v>46153</v>
+      </c>
+      <c r="J29" s="23">
+        <v>46173</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="71"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="25"/>
+    </row>
+    <row r="30" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="127" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="128"/>
+      <c r="D30" s="128"/>
+      <c r="E30" s="129"/>
+      <c r="F30" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="64">
+        <v>0</v>
+      </c>
+      <c r="H30" s="64">
+        <v>10</v>
+      </c>
+      <c r="I30" s="23">
+        <v>46153</v>
+      </c>
+      <c r="J30" s="23">
+        <v>46173</v>
+      </c>
+      <c r="K30" s="2"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
+      <c r="W30" s="25"/>
+      <c r="X30" s="40"/>
+      <c r="Y30" s="40"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="25"/>
+    </row>
+    <row r="31" spans="2:28" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="65">
+        <f>SUM(G32:G33)</f>
         <v>25</v>
       </c>
-      <c r="G17" s="94">
+      <c r="H31" s="65">
+        <f>SUM(H32:H33)</f>
+        <v>15</v>
+      </c>
+      <c r="I31" s="58">
+        <v>46159</v>
+      </c>
+      <c r="J31" s="58">
+        <v>46188</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="25"/>
+      <c r="W31" s="25"/>
+      <c r="X31" s="67"/>
+      <c r="Y31" s="67"/>
+      <c r="Z31" s="67"/>
+      <c r="AA31" s="67"/>
+      <c r="AB31" s="68"/>
+    </row>
+    <row r="32" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="66">
+        <v>10</v>
+      </c>
+      <c r="H32" s="66">
+        <v>15</v>
+      </c>
+      <c r="I32" s="59">
+        <v>46159</v>
+      </c>
+      <c r="J32" s="59">
+        <v>46188</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="25"/>
+      <c r="W32" s="25"/>
+      <c r="X32" s="69"/>
+      <c r="Y32" s="69"/>
+      <c r="Z32" s="69"/>
+      <c r="AA32" s="69"/>
+      <c r="AB32" s="70"/>
+    </row>
+    <row r="33" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="86" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="66">
+        <v>15</v>
+      </c>
+      <c r="H33" s="66">
+        <v>0</v>
+      </c>
+      <c r="I33" s="59">
+        <v>46159</v>
+      </c>
+      <c r="J33" s="59">
+        <v>46188</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
+      <c r="W33" s="25"/>
+      <c r="X33" s="69"/>
+      <c r="Y33" s="69"/>
+      <c r="Z33" s="69"/>
+      <c r="AA33" s="69"/>
+      <c r="AB33" s="70"/>
+    </row>
+    <row r="34" spans="2:28" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="56">
+        <f>SUM(G35:G37)</f>
+        <v>40</v>
+      </c>
+      <c r="H34" s="56">
+        <f>SUM(H35:H37)</f>
         <v>35</v>
       </c>
-      <c r="H17" s="94">
-        <v>75</v>
-      </c>
-      <c r="I17" s="21">
-        <v>46064</v>
-      </c>
-      <c r="J17" s="75">
-        <v>46106</v>
-      </c>
-      <c r="L17" s="66"/>
-      <c r="M17" s="66"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="76"/>
-      <c r="S17" s="76"/>
-      <c r="T17" s="76"/>
-      <c r="U17" s="76"/>
-      <c r="V17" s="69"/>
-      <c r="W17" s="69"/>
-      <c r="X17" s="69"/>
-      <c r="Y17" s="69"/>
-      <c r="Z17" s="69"/>
-      <c r="AA17" s="69"/>
-      <c r="AB17" s="66"/>
-    </row>
-    <row r="18" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="12" t="s">
+      <c r="I34" s="8">
+        <v>46163</v>
+      </c>
+      <c r="J34" s="8">
+        <v>46188</v>
+      </c>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="28"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28"/>
+      <c r="Y34" s="41"/>
+      <c r="Z34" s="41"/>
+      <c r="AA34" s="41"/>
+      <c r="AB34" s="41"/>
+    </row>
+    <row r="35" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" s="53">
+        <v>10</v>
+      </c>
+      <c r="H35" s="53">
+        <v>20</v>
+      </c>
+      <c r="I35" s="42">
+        <v>46163</v>
+      </c>
+      <c r="J35" s="24">
+        <v>46174</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="28"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28"/>
+      <c r="Y35" s="43"/>
+      <c r="Z35" s="43"/>
+      <c r="AA35" s="28"/>
+      <c r="AB35" s="25"/>
+    </row>
+    <row r="36" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="53">
+        <v>25</v>
+      </c>
+      <c r="H36" s="53">
+        <v>10</v>
+      </c>
+      <c r="I36" s="24">
+        <v>46174</v>
+      </c>
+      <c r="J36" s="24">
+        <v>46183</v>
+      </c>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
+      <c r="V36" s="28"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="43"/>
+      <c r="AA36" s="43"/>
+      <c r="AB36" s="25"/>
+    </row>
+    <row r="37" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="73" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="75"/>
+      <c r="F37" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="53">
+        <v>5</v>
+      </c>
+      <c r="H37" s="53">
+        <v>5</v>
+      </c>
+      <c r="I37" s="24">
+        <v>46183</v>
+      </c>
+      <c r="J37" s="24">
+        <v>46188</v>
+      </c>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="25"/>
+    </row>
+    <row r="38" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="73" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="74"/>
+      <c r="D38" s="74"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="94">
-        <v>15</v>
-      </c>
-      <c r="H18" s="94">
-        <v>15</v>
-      </c>
-      <c r="I18" s="20">
-        <v>46107</v>
-      </c>
-      <c r="J18" s="20">
-        <v>46122</v>
-      </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="66"/>
-      <c r="T18" s="66"/>
-      <c r="U18" s="76"/>
-      <c r="V18" s="76"/>
-      <c r="W18" s="69"/>
-      <c r="X18" s="69"/>
-      <c r="Y18" s="69"/>
-      <c r="Z18" s="69"/>
-      <c r="AA18" s="69"/>
-      <c r="AB18" s="66"/>
-    </row>
-    <row r="19" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="94">
-        <v>25</v>
-      </c>
-      <c r="H19" s="94">
-        <v>25</v>
-      </c>
-      <c r="I19" s="20">
-        <v>46123</v>
-      </c>
-      <c r="J19" s="20">
-        <v>46132</v>
-      </c>
-      <c r="K19" s="2"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66"/>
-      <c r="T19" s="66"/>
-      <c r="U19" s="69"/>
-      <c r="V19" s="76"/>
-      <c r="W19" s="76"/>
-      <c r="X19" s="69"/>
-      <c r="Y19" s="69"/>
-      <c r="Z19" s="69"/>
-      <c r="AA19" s="69"/>
-      <c r="AB19" s="66"/>
-    </row>
-    <row r="20" spans="2:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="95">
-        <f>SUM(G21:G22)</f>
-        <v>25</v>
-      </c>
-      <c r="H20" s="95">
-        <f>SUM(H21:H22)</f>
-        <v>35</v>
-      </c>
-      <c r="I20" s="7">
-        <v>46133</v>
-      </c>
-      <c r="J20" s="7">
-        <v>46162</v>
-      </c>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="66"/>
-      <c r="T20" s="66"/>
-      <c r="U20" s="66"/>
-      <c r="V20" s="66"/>
-      <c r="W20" s="78"/>
-      <c r="X20" s="70"/>
-      <c r="Y20" s="77"/>
-      <c r="Z20" s="71"/>
-      <c r="AA20" s="71"/>
-      <c r="AB20" s="66"/>
-    </row>
-    <row r="21" spans="2:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="96">
-        <v>15</v>
-      </c>
-      <c r="H21" s="96">
-        <v>25</v>
-      </c>
-      <c r="I21" s="79">
-        <v>46133</v>
-      </c>
-      <c r="J21" s="23">
-        <v>46152</v>
-      </c>
-      <c r="K21" s="2"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="66"/>
-      <c r="U21" s="66"/>
-      <c r="V21" s="66"/>
-      <c r="W21" s="80"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="69"/>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="69"/>
-      <c r="AB21" s="66"/>
-    </row>
-    <row r="22" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="96">
+      <c r="G38" s="53">
+        <v>5</v>
+      </c>
+      <c r="H38" s="53">
         <v>10</v>
       </c>
-      <c r="H22" s="96">
-        <v>10</v>
-      </c>
-      <c r="I22" s="22">
-        <v>46153</v>
-      </c>
-      <c r="J22" s="22">
-        <v>46162</v>
-      </c>
-      <c r="K22" s="2"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="81"/>
-      <c r="Y22" s="81"/>
-      <c r="Z22" s="71"/>
-      <c r="AA22" s="71"/>
-      <c r="AB22" s="66"/>
-    </row>
-    <row r="23" spans="2:28" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="97">
-        <f>SUM(G24:G26)</f>
-        <v>50</v>
-      </c>
-      <c r="H23" s="97">
-        <f>SUM(H24:H26)</f>
-        <v>35</v>
-      </c>
-      <c r="I23" s="8">
+      <c r="I38" s="24">
         <v>46163</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J38" s="24">
         <v>46188</v>
       </c>
-      <c r="L23" s="69"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="69"/>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="69"/>
-      <c r="R23" s="69"/>
-      <c r="S23" s="69"/>
-      <c r="T23" s="69"/>
-      <c r="U23" s="69"/>
-      <c r="V23" s="69"/>
-      <c r="W23" s="69"/>
-      <c r="X23" s="69"/>
-      <c r="Y23" s="82"/>
-      <c r="Z23" s="82"/>
-      <c r="AA23" s="82"/>
-      <c r="AB23" s="82"/>
-    </row>
-    <row r="24" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="98">
-        <v>10</v>
-      </c>
-      <c r="H24" s="98">
-        <v>20</v>
-      </c>
-      <c r="I24" s="83">
-        <v>46163</v>
-      </c>
-      <c r="J24" s="24">
-        <v>46174</v>
-      </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="69"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="69"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="69"/>
-      <c r="R24" s="69"/>
-      <c r="S24" s="69"/>
-      <c r="T24" s="69"/>
-      <c r="U24" s="69"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="69"/>
-      <c r="X24" s="69"/>
-      <c r="Y24" s="84"/>
-      <c r="Z24" s="84"/>
-      <c r="AA24" s="69"/>
-      <c r="AB24" s="66"/>
-    </row>
-    <row r="25" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="98">
-        <v>35</v>
-      </c>
-      <c r="H25" s="98">
-        <v>10</v>
-      </c>
-      <c r="I25" s="24">
-        <v>46174</v>
-      </c>
-      <c r="J25" s="24">
-        <v>46183</v>
-      </c>
-      <c r="L25" s="69"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="69"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="69"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="69"/>
-      <c r="U25" s="69"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="69"/>
-      <c r="X25" s="69"/>
-      <c r="Y25" s="69"/>
-      <c r="Z25" s="84"/>
-      <c r="AA25" s="84"/>
-      <c r="AB25" s="66"/>
-    </row>
-    <row r="26" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="98">
-        <v>5</v>
-      </c>
-      <c r="H26" s="98">
-        <v>5</v>
-      </c>
-      <c r="I26" s="24">
-        <v>46183</v>
-      </c>
-      <c r="J26" s="24">
-        <v>46188</v>
-      </c>
-      <c r="K26" s="2"/>
-      <c r="L26" s="69"/>
-      <c r="M26" s="69"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="69"/>
-      <c r="P26" s="69"/>
-      <c r="Q26" s="69"/>
-      <c r="R26" s="69"/>
-      <c r="S26" s="69"/>
-      <c r="T26" s="69"/>
-      <c r="U26" s="69"/>
-      <c r="V26" s="69"/>
-      <c r="W26" s="69"/>
-      <c r="X26" s="69"/>
-      <c r="Y26" s="69"/>
-      <c r="Z26" s="69"/>
-      <c r="AA26" s="84"/>
-      <c r="AB26" s="84"/>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="G27" s="99">
-        <f>SUM(G23,G20,G15,G10)</f>
+      <c r="K38" s="2"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
+      <c r="V38" s="28"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28"/>
+      <c r="Y38" s="43"/>
+      <c r="Z38" s="43"/>
+      <c r="AA38" s="43"/>
+      <c r="AB38" s="43"/>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="G39" s="54">
+        <f>SUM(G34,G26,G18,G10,G31)</f>
         <v>270</v>
       </c>
-      <c r="H27" s="99">
-        <f>SUM(H23,H20,H15,H10)</f>
+      <c r="H39" s="54">
+        <f>SUM(H34,H26,H18,H10,H31)</f>
         <v>270</v>
       </c>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4"/>
-      <c r="Y27" s="4"/>
-      <c r="Z27" s="4"/>
-      <c r="AA27" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="35">
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B27:E27"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B1:D2"/>
@@ -2230,18 +2865,26 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B15:E15"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2250,6 +2893,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A353B9F84D3FE49ACDE5D3400E1BB29" ma:contentTypeVersion="4" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="61b4832fd582f590a18ae35661cb8638">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="949fa741-de20-450d-902f-ecc64febdd8b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="11425ee04ce26f6333e320263679ea7e" ns2:_="">
     <xsd:import namespace="949fa741-de20-450d-902f-ecc64febdd8b"/>
@@ -2393,22 +3045,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D674519C-4A7E-480E-A966-4DE708160A61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0071880-ECB7-40CA-8BDD-66BBAD2E8275}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2426,26 +3077,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E73C2513-9015-4353-8180-66C0F7D4ED7E}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="949fa741-de20-450d-902f-ecc64febdd8b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D674519C-4A7E-480E-A966-4DE708160A61}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>